--- a/docs/目标场景性能测试.xlsx
+++ b/docs/目标场景性能测试.xlsx
@@ -1,42 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailustceducn-my.sharepoint.com/personal/via_mail_ustc_edu_cn/Documents/DBY/kylab/胡杨林基金/ccfhw2025/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{2575059E-D47F-45FA-9957-F0A16E569E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC5E5A64-E317-4BC6-82C2-B8A7E576ABF9}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{2575059E-D47F-45FA-9957-F0A16E569E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C53873D-DE3B-4CE8-A335-B00FE8162AC9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="腾讯文档-丁伯尧测试结果" sheetId="1" r:id="rId1"/>
+    <sheet name="WPS-徐铭凯测试结果" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="52">
   <si>
     <t>测试场景</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,10 +41,6 @@
   </si>
   <si>
     <t>性能结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总计</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -125,13 +111,112 @@
   <si>
     <t>windows11, x86_64, 基于 138.0.3351.109 版本的edge浏览器</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总计(ms)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>统计脚本执行时间的具体拆解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他硬件平台上的性能统计，做对比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Your Projects - S4Plus Overleaf, Online LaTeX Editor</t>
+  </si>
+  <si>
+    <t>打开、编辑文字、编译</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多开</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试网址：www.kdocs.cn（WPS在线编辑PPT）</t>
+  </si>
+  <si>
+    <t>测试在https://www.kdocs.cn/l/cuh8SYwgFRbh上进行</t>
+  </si>
+  <si>
+    <t>1. 选中第一页的文字，通过鼠标点击更改字号：40 -&gt; 72</t>
+  </si>
+  <si>
+    <t>轮次\用时</t>
+  </si>
+  <si>
+    <t>脚本执行</t>
+  </si>
+  <si>
+    <t>渲染</t>
+  </si>
+  <si>
+    <t>加载</t>
+  </si>
+  <si>
+    <t>系统</t>
+  </si>
+  <si>
+    <t>上色</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
+  <si>
+    <t>记录标准：从鼠标点击事件开始，到字号更改显示在屏幕上结束</t>
+  </si>
+  <si>
+    <t>平均</t>
+  </si>
+  <si>
+    <t>2. 将第一页的文字粘贴到第二页的末尾（右键、鼠标点击）</t>
+  </si>
+  <si>
+    <t>记录标准：从鼠标点击事件开始，到文字添加显示在屏幕上结束</t>
+  </si>
+  <si>
+    <t>注意到这个过程中有很多“空闲”时间，值得研究</t>
+  </si>
+  <si>
+    <t>3. 在PPT末尾新增空白页</t>
+  </si>
+  <si>
+    <t>Terminal 1</t>
+  </si>
+  <si>
+    <t>记录标准：从鼠标点击事件开始，到：</t>
+  </si>
+  <si>
+    <t>1) 屏幕中央变为空白页结束；</t>
+  </si>
+  <si>
+    <t>2) 左下角出现新页面，且最下方的提示文字消失结束</t>
+  </si>
+  <si>
+    <t>Terminal 2</t>
+  </si>
+  <si>
+    <t>浏览器内核：Chrome 138.0.0.0</t>
+  </si>
+  <si>
+    <t>内存占用：约为3000MB</t>
+  </si>
+  <si>
+    <t>系统信息：Windows10，Intel i7-7500U CPU @ 2.70GHz</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,6 +248,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -185,7 +278,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -199,6 +292,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -213,6 +313,21 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -236,16 +351,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>596347</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2063</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>177926</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>40898</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>246208</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>143561</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -268,8 +383,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12058650" y="542925"/>
-          <a:ext cx="8017001" cy="4384298"/>
+          <a:off x="15659651" y="178759"/>
+          <a:ext cx="7601166" cy="4205498"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -280,16 +395,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>23676</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>570329</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>150054</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>273176</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>141208</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>157220</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>85991</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -312,8 +427,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11691801" y="5276850"/>
-          <a:ext cx="8479100" cy="4637008"/>
+          <a:off x="15633633" y="4567445"/>
+          <a:ext cx="8200804" cy="4530024"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -331,7 +446,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>177926</xdr:colOff>
+      <xdr:colOff>12274</xdr:colOff>
       <xdr:row>108</xdr:row>
       <xdr:rowOff>131692</xdr:rowOff>
     </xdr:to>
@@ -374,8 +489,8 @@
       <xdr:rowOff>125432</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>54101</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>551058</xdr:colOff>
       <xdr:row>80</xdr:row>
       <xdr:rowOff>74543</xdr:rowOff>
     </xdr:to>
@@ -676,79 +791,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.25" customWidth="1"/>
-    <col min="2" max="2" width="28.875" customWidth="1"/>
+    <col min="1" max="1" width="36.1640625" customWidth="1"/>
+    <col min="2" max="2" width="45.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="2"/>
     <col min="11" max="11" width="9" style="4"/>
+    <col min="13" max="13" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="4" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="M4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-    </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>5</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>6</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>7</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>8</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>9</v>
       </c>
-      <c r="J5" t="s">
-        <v>10</v>
-      </c>
       <c r="K5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="2">
@@ -780,9 +902,9 @@
         <v>0.88628370457209849</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="9"/>
-      <c r="B7" s="8"/>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="12"/>
+      <c r="B7" s="11"/>
       <c r="C7" s="2">
         <v>2</v>
       </c>
@@ -812,9 +934,9 @@
         <v>0.8496151568975725</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="9"/>
-      <c r="B8" s="8"/>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="12"/>
+      <c r="B8" s="11"/>
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -844,9 +966,9 @@
         <v>0.90717821782178221</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="8"/>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="11"/>
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -876,9 +998,9 @@
         <v>0.88943623426382046</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
-      <c r="B10" s="8"/>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="11"/>
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -908,22 +1030,22 @@
         <v>0.88403041825095052</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="9"/>
-      <c r="B11" s="8"/>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="11"/>
       <c r="C11" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1">
         <f>AVERAGE(D6:D10)</f>
         <v>1683.2</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" ref="E11:J11" si="1">AVERAGE(E6:E10)</f>
+        <f>AVERAGE(E6:E10)</f>
         <v>1486.6</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="F11:J11" si="1">AVERAGE(F6:F10)</f>
         <v>50</v>
       </c>
       <c r="G11" s="1">
@@ -947,12 +1069,12 @@
         <v>0.88319866920152079</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>14</v>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>13</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -983,9 +1105,9 @@
         <v>0.54947916666666663</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="9"/>
-      <c r="B13" s="8"/>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="12"/>
+      <c r="B13" s="11"/>
       <c r="C13" s="2">
         <v>2</v>
       </c>
@@ -1015,9 +1137,9 @@
         <v>0.66485013623978206</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="9"/>
-      <c r="B14" s="8"/>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+      <c r="B14" s="11"/>
       <c r="C14" s="2">
         <v>3</v>
       </c>
@@ -1047,9 +1169,9 @@
         <v>0.50967741935483868</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="9"/>
-      <c r="B15" s="8"/>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="2">
         <v>4</v>
       </c>
@@ -1079,9 +1201,9 @@
         <v>0.46644295302013422</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="9"/>
-      <c r="B16" s="8"/>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="12"/>
+      <c r="B16" s="11"/>
       <c r="C16" s="2">
         <v>5</v>
       </c>
@@ -1111,11 +1233,11 @@
         <v>0.6160714285714286</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="9"/>
-      <c r="B17" s="8"/>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="12"/>
+      <c r="B17" s="11"/>
       <c r="C17" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1">
         <f>AVERAGE(D12:D16)</f>
@@ -1150,12 +1272,12 @@
         <v>0.56578171091445428</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="9" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -1186,9 +1308,9 @@
         <v>0.428226779252111</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="9"/>
-      <c r="B19" s="8"/>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="12"/>
+      <c r="B19" s="11"/>
       <c r="C19" s="2">
         <v>2</v>
       </c>
@@ -1218,9 +1340,9 @@
         <v>0.60964912280701755</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="9"/>
-      <c r="B20" s="8"/>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="12"/>
+      <c r="B20" s="11"/>
       <c r="C20" s="2">
         <v>3</v>
       </c>
@@ -1250,9 +1372,9 @@
         <v>0.62383177570093462</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="9"/>
-      <c r="B21" s="8"/>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="12"/>
+      <c r="B21" s="11"/>
       <c r="C21" s="2">
         <v>4</v>
       </c>
@@ -1282,9 +1404,9 @@
         <v>0.44617784711388453</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="9"/>
-      <c r="B22" s="8"/>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="12"/>
+      <c r="B22" s="11"/>
       <c r="C22" s="2">
         <v>5</v>
       </c>
@@ -1314,10 +1436,11 @@
         <v>0.53797468354430378</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="9"/>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="12"/>
+      <c r="B23" s="11"/>
       <c r="C23" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23" s="1">
         <f>AVERAGE(D18:D22)</f>
@@ -1352,12 +1475,12 @@
         <v>0.50954738330975946</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="8" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>15</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -1388,9 +1511,9 @@
         <v>0.73443983402489632</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="7"/>
-      <c r="B25" s="8"/>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="11"/>
       <c r="C25" s="2">
         <v>2</v>
       </c>
@@ -1420,9 +1543,9 @@
         <v>0.65551839464882944</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="7"/>
-      <c r="B26" s="8"/>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
       <c r="C26" s="2">
         <v>3</v>
       </c>
@@ -1452,9 +1575,9 @@
         <v>0.53177966101694918</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="8"/>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="11"/>
       <c r="C27" s="2">
         <v>4</v>
       </c>
@@ -1484,9 +1607,9 @@
         <v>0.68433734939759039</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="8"/>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
       <c r="C28" s="2">
         <v>5</v>
       </c>
@@ -1516,11 +1639,11 @@
         <v>0.57831325301204817</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="7"/>
-      <c r="B29" s="8"/>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D29" s="1">
         <f>AVERAGE(D24:D28)</f>
@@ -1553,6 +1676,22 @@
       <c r="K29" s="6">
         <f t="shared" si="0"/>
         <v>0.63850000000000007</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1566,8 +1705,8 @@
     <mergeCell ref="A24:A29"/>
     <mergeCell ref="B24:B29"/>
     <mergeCell ref="A18:A23"/>
-    <mergeCell ref="B18:B22"/>
     <mergeCell ref="B6:B11"/>
+    <mergeCell ref="B18:B23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -1575,8 +1714,897 @@
     <hyperlink ref="A24" r:id="rId2" xr:uid="{57411C43-2BD7-4C87-AB8D-FF27A0A00050}"/>
     <hyperlink ref="A12" r:id="rId3" xr:uid="{DB33AC82-45D0-4B56-AF84-581A45A66C91}"/>
     <hyperlink ref="A18" r:id="rId4" xr:uid="{0B3BC045-2C7E-49B2-A173-34865230C1C2}"/>
+    <hyperlink ref="A30" r:id="rId5" display="http://222.195.92.204:9001/project" xr:uid="{AB263146-A2A8-4A41-BEFD-A41129533A22}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId6"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B69129-BCB1-426E-ACA7-A7D5B9EA4C01}">
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7">
+        <v>151</v>
+      </c>
+      <c r="E5" s="7">
+        <v>56</v>
+      </c>
+      <c r="F5" s="7">
+        <v>6</v>
+      </c>
+      <c r="G5" s="7">
+        <v>4</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3</v>
+      </c>
+      <c r="I5" s="7">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="7">
+        <v>2</v>
+      </c>
+      <c r="D6" s="7">
+        <v>137</v>
+      </c>
+      <c r="E6" s="7">
+        <v>23</v>
+      </c>
+      <c r="F6" s="7">
+        <v>5</v>
+      </c>
+      <c r="G6" s="7">
+        <v>3</v>
+      </c>
+      <c r="H6" s="7">
+        <v>2</v>
+      </c>
+      <c r="I6" s="7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="7">
+        <v>3</v>
+      </c>
+      <c r="D7" s="7">
+        <v>131</v>
+      </c>
+      <c r="E7" s="7">
+        <v>24</v>
+      </c>
+      <c r="F7" s="7">
+        <v>5</v>
+      </c>
+      <c r="G7" s="7">
+        <v>4</v>
+      </c>
+      <c r="H7" s="7">
+        <v>4</v>
+      </c>
+      <c r="I7" s="7">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="7">
+        <v>4</v>
+      </c>
+      <c r="D8" s="7">
+        <v>176</v>
+      </c>
+      <c r="E8" s="7">
+        <v>36</v>
+      </c>
+      <c r="F8" s="7">
+        <v>5</v>
+      </c>
+      <c r="G8" s="7">
+        <v>4</v>
+      </c>
+      <c r="H8" s="7">
+        <v>4</v>
+      </c>
+      <c r="I8" s="7">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="7">
+        <v>5</v>
+      </c>
+      <c r="D9" s="7">
+        <v>150</v>
+      </c>
+      <c r="E9" s="7">
+        <v>20</v>
+      </c>
+      <c r="F9" s="7">
+        <v>5</v>
+      </c>
+      <c r="G9" s="7">
+        <v>3</v>
+      </c>
+      <c r="H9" s="7">
+        <v>3</v>
+      </c>
+      <c r="I9" s="7">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="8">
+        <f t="shared" ref="D10:I10" si="0">AVERAGE(D5:D9)</f>
+        <v>149</v>
+      </c>
+      <c r="E10" s="8">
+        <f t="shared" si="0"/>
+        <v>31.8</v>
+      </c>
+      <c r="F10" s="8">
+        <f t="shared" si="0"/>
+        <v>5.2</v>
+      </c>
+      <c r="G10" s="8">
+        <f t="shared" si="0"/>
+        <v>3.6</v>
+      </c>
+      <c r="H10" s="8">
+        <f t="shared" si="0"/>
+        <v>3.2</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>195.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>72</v>
+      </c>
+      <c r="E13" s="7">
+        <v>27</v>
+      </c>
+      <c r="F13" s="7">
+        <v>15</v>
+      </c>
+      <c r="G13" s="7">
+        <v>14</v>
+      </c>
+      <c r="H13" s="7">
+        <v>4</v>
+      </c>
+      <c r="I13" s="7">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="7">
+        <v>2</v>
+      </c>
+      <c r="D14" s="7">
+        <v>76</v>
+      </c>
+      <c r="E14" s="7">
+        <v>37</v>
+      </c>
+      <c r="F14" s="7">
+        <v>16</v>
+      </c>
+      <c r="G14" s="7">
+        <v>15</v>
+      </c>
+      <c r="H14" s="7">
+        <v>4</v>
+      </c>
+      <c r="I14" s="7">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="7">
+        <v>3</v>
+      </c>
+      <c r="D15" s="7">
+        <v>81</v>
+      </c>
+      <c r="E15" s="7">
+        <v>32</v>
+      </c>
+      <c r="F15" s="7">
+        <v>18</v>
+      </c>
+      <c r="G15" s="7">
+        <v>17</v>
+      </c>
+      <c r="H15" s="7">
+        <v>5</v>
+      </c>
+      <c r="I15" s="7">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="7">
+        <v>4</v>
+      </c>
+      <c r="D16" s="7">
+        <v>72</v>
+      </c>
+      <c r="E16" s="7">
+        <v>28</v>
+      </c>
+      <c r="F16" s="7">
+        <v>16</v>
+      </c>
+      <c r="G16" s="7">
+        <v>8</v>
+      </c>
+      <c r="H16" s="7">
+        <v>4</v>
+      </c>
+      <c r="I16" s="7">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="7">
+        <v>5</v>
+      </c>
+      <c r="D17" s="7">
+        <v>72</v>
+      </c>
+      <c r="E17" s="7">
+        <v>28</v>
+      </c>
+      <c r="F17" s="7">
+        <v>18</v>
+      </c>
+      <c r="G17" s="7">
+        <v>12</v>
+      </c>
+      <c r="H17" s="7">
+        <v>4</v>
+      </c>
+      <c r="I17" s="7">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="8">
+        <f t="shared" ref="D18:I18" si="1">AVERAGE(D13:D17)</f>
+        <v>74.599999999999994</v>
+      </c>
+      <c r="E18" s="8">
+        <f t="shared" si="1"/>
+        <v>30.4</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" si="1"/>
+        <v>16.600000000000001</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="1"/>
+        <v>13.2</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="1"/>
+        <v>4.2</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="1"/>
+        <v>232.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="7">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7">
+        <v>68</v>
+      </c>
+      <c r="E21" s="7">
+        <v>15</v>
+      </c>
+      <c r="F21" s="7">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7">
+        <v>8</v>
+      </c>
+      <c r="H21" s="7">
+        <v>3</v>
+      </c>
+      <c r="I21" s="7">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="7">
+        <v>2</v>
+      </c>
+      <c r="D22" s="7">
+        <v>60</v>
+      </c>
+      <c r="E22" s="7">
+        <v>13</v>
+      </c>
+      <c r="F22" s="7">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7">
+        <v>9</v>
+      </c>
+      <c r="H22" s="7">
+        <v>3</v>
+      </c>
+      <c r="I22" s="7">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="16"/>
+      <c r="C23" s="7">
+        <v>3</v>
+      </c>
+      <c r="D23" s="7">
+        <v>62</v>
+      </c>
+      <c r="E23" s="7">
+        <v>13</v>
+      </c>
+      <c r="F23" s="7">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7">
+        <v>8</v>
+      </c>
+      <c r="H23" s="7">
+        <v>3</v>
+      </c>
+      <c r="I23" s="7">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="7">
+        <v>4</v>
+      </c>
+      <c r="D24" s="7">
+        <v>66</v>
+      </c>
+      <c r="E24" s="7">
+        <v>13</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7">
+        <v>8</v>
+      </c>
+      <c r="H24" s="7">
+        <v>3</v>
+      </c>
+      <c r="I24" s="7">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="7">
+        <v>5</v>
+      </c>
+      <c r="D25" s="7">
+        <v>66</v>
+      </c>
+      <c r="E25" s="7">
+        <v>13</v>
+      </c>
+      <c r="F25" s="7">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7">
+        <v>8</v>
+      </c>
+      <c r="H25" s="7">
+        <v>3</v>
+      </c>
+      <c r="I25" s="7">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="8">
+        <f t="shared" ref="D26:I26" si="2">AVERAGE(D21:D25)</f>
+        <v>64.400000000000006</v>
+      </c>
+      <c r="E26" s="8">
+        <f t="shared" si="2"/>
+        <v>13.4</v>
+      </c>
+      <c r="F26" s="8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="8">
+        <f t="shared" si="2"/>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H26" s="8">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="I26" s="8">
+        <f t="shared" si="2"/>
+        <v>166.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="16"/>
+      <c r="B28" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="7">
+        <v>1</v>
+      </c>
+      <c r="D29" s="7">
+        <v>197</v>
+      </c>
+      <c r="E29" s="7">
+        <v>61</v>
+      </c>
+      <c r="F29" s="7">
+        <v>1</v>
+      </c>
+      <c r="G29" s="7">
+        <v>15</v>
+      </c>
+      <c r="H29" s="7">
+        <v>7</v>
+      </c>
+      <c r="I29" s="7">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="16"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="7">
+        <v>2</v>
+      </c>
+      <c r="D30" s="7">
+        <v>183</v>
+      </c>
+      <c r="E30" s="7">
+        <v>60</v>
+      </c>
+      <c r="F30" s="7">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7">
+        <v>15</v>
+      </c>
+      <c r="H30" s="7">
+        <v>7</v>
+      </c>
+      <c r="I30" s="7">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="16"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="7">
+        <v>3</v>
+      </c>
+      <c r="D31" s="7">
+        <v>197</v>
+      </c>
+      <c r="E31" s="7">
+        <v>60</v>
+      </c>
+      <c r="F31" s="7">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7">
+        <v>14</v>
+      </c>
+      <c r="H31" s="7">
+        <v>6</v>
+      </c>
+      <c r="I31" s="7">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="7">
+        <v>4</v>
+      </c>
+      <c r="D32" s="7">
+        <v>191</v>
+      </c>
+      <c r="E32" s="7">
+        <v>57</v>
+      </c>
+      <c r="F32" s="7">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7">
+        <v>15</v>
+      </c>
+      <c r="H32" s="7">
+        <v>8</v>
+      </c>
+      <c r="I32" s="7">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="7">
+        <v>5</v>
+      </c>
+      <c r="D33" s="7">
+        <v>196</v>
+      </c>
+      <c r="E33" s="7">
+        <v>67</v>
+      </c>
+      <c r="F33" s="7">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7">
+        <v>15</v>
+      </c>
+      <c r="H33" s="7">
+        <v>8</v>
+      </c>
+      <c r="I33" s="7">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="8">
+        <f t="shared" ref="D34:I34" si="3">AVERAGE(D29:D33)</f>
+        <v>192.8</v>
+      </c>
+      <c r="E34" s="8">
+        <f t="shared" si="3"/>
+        <v>61</v>
+      </c>
+      <c r="F34" s="8">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="G34" s="8">
+        <f t="shared" si="3"/>
+        <v>14.8</v>
+      </c>
+      <c r="H34" s="8">
+        <f t="shared" si="3"/>
+        <v>7.2</v>
+      </c>
+      <c r="I34" s="8">
+        <f t="shared" si="3"/>
+        <v>354.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="16"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>